--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/5-Project/Localization.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/5-Project/Localization.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I30"/>
+  <dimension ref="B2:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -582,70 +582,75 @@
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Method String Greeting(String name)</t>
-        </is>
-      </c>
+          <t>Spreadsheet String Greeting(String name)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>return msg("greeting", name);</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>= msg("greeting", name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Test Greeting GreetingLocalizedTest</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>_context_.locale</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Locale</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Greeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Ann</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Hello, Ann!</t>
         </is>
       </c>
     </row>
@@ -655,14 +660,10 @@
           <t>Ann</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Bonjour, Ann !</t>
+          <t>Hello, Ann!</t>
         </is>
       </c>
     </row>
@@ -674,7 +675,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>fr-CA</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -691,12 +692,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>de-DE</t>
+          <t>fr-CA</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hallo, Ann!</t>
+          <t>Bonjour, Ann !</t>
         </is>
       </c>
     </row>
@@ -708,146 +709,138 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Hallo, Ann!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
           <t>uk-UA</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Hello, Ann!</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Spreadsheet SpreadsheetResult OrderMessages(String orderId, Double amount)</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+      <c r="C21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>= msg("order.total", orderId, amount)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>= msg("order.total", orderId, amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>Farewell</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>= msg("farewell")</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Test OrderMessages OrderMessagesTest</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>orderId</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>_context_.locale</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>_res_.$Total</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>_res_.$Farewell</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Locale</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Farewell</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Order A-1 costs 25 USD.</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Goodbye</t>
         </is>
       </c>
     </row>
@@ -862,12 +855,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>La commande A-1 coûte 25 USD.</t>
+          <t>Order A-1 costs 25 USD.</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -887,26 +880,52 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>La commande A-1 coûte 25 USD.</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Goodbye</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
           <t>de-DE</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Bestellung A-1 kostet 25 USD.</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Auf Wiedersehen</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B11:D11"/>
+  <mergeCells count="6">
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B26:F26"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
